--- a/docentes/Rodríguez Román Leticia - Estadisticos 20212.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20212.xlsx
@@ -471,16 +471,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -494,16 +497,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>86.11</v>
+      </c>
+      <c r="H3">
+        <v>5.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -517,16 +523,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>87.88</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +591,7 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -605,7 +614,7 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -628,7 +637,7 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -687,16 +696,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -710,16 +722,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>86.11</v>
+      </c>
+      <c r="H3">
+        <v>5.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -733,16 +748,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>87.88</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20212.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
   </si>
 </sst>
 </file>
@@ -770,7 +779,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -800,6 +809,29 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920362</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20212.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="59">
   <si>
     <t>Mat</t>
   </si>
@@ -73,13 +73,127 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANDRIA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>VELAZQEZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>TEPEPA</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ALONSO</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>JOSE MATEO</t>
+  </si>
+  <si>
+    <t>MONSERRATH YARETZY</t>
+  </si>
+  <si>
+    <t>EVELYN IVETH</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>LIZBET</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
+  </si>
+  <si>
+    <t>JAROMI YAJAIRA</t>
+  </si>
+  <si>
+    <t>EDGAR RAMSES</t>
+  </si>
+  <si>
+    <t>PAULINA</t>
   </si>
 </sst>
 </file>
@@ -597,16 +711,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>65.63</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -620,16 +737,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>58.33</v>
+      </c>
+      <c r="H3">
+        <v>5.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -708,16 +828,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>87.5</v>
+        <v>65.63</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -734,13 +854,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>86.11</v>
+        <v>58.33</v>
       </c>
       <c r="H3">
         <v>5.9</v>
@@ -779,7 +899,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -811,16 +931,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920362</v>
+        <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -830,6 +950,305 @@
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920013</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920021</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920029</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920393</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920183</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920111</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920028</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920369</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920167</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920172</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920180</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920373</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920154</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20212.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="69">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,9 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
     <t>VALENTE</t>
   </si>
   <si>
@@ -115,6 +118,15 @@
     <t>VELAZQEZ</t>
   </si>
   <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
@@ -133,6 +145,9 @@
     <t>TEPEPA</t>
   </si>
   <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
     <t>GAMEZ</t>
   </si>
   <si>
@@ -154,6 +169,9 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
     <t>CRISTOPHER ALAIN</t>
   </si>
   <si>
@@ -172,6 +190,9 @@
     <t>EVELYN IVETH</t>
   </si>
   <si>
+    <t>BENY ALEXANDER</t>
+  </si>
+  <si>
     <t>ABIUD</t>
   </si>
   <si>
@@ -194,6 +215,15 @@
   </si>
   <si>
     <t>PAULINA</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>ROSA ISELA</t>
   </si>
 </sst>
 </file>
@@ -763,16 +793,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>63.64</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -880,16 +913,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>87.88</v>
+        <v>63.64</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>5.8</v>
       </c>
     </row>
   </sheetData>
@@ -899,7 +932,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -937,10 +970,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -960,10 +993,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -983,10 +1016,10 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1006,10 +1039,10 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1029,10 +1062,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1052,10 +1085,10 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1069,16 +1102,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920111</v>
+        <v>20330051920109</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1092,45 +1125,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920028</v>
+        <v>20330051920111</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920369</v>
+        <v>20330051920028</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1138,16 +1171,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920167</v>
+        <v>20330051920369</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1161,16 +1194,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920172</v>
+        <v>20330051920167</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1184,16 +1217,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920180</v>
+        <v>20330051920172</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1207,16 +1240,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920373</v>
+        <v>20330051920180</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1230,16 +1263,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920154</v>
+        <v>20330051920373</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1248,6 +1281,98 @@
         <v>10</v>
       </c>
       <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920154</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920046</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920101</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920107</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20212.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="100">
   <si>
     <t>Mat</t>
   </si>
@@ -73,70 +73,145 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>ADELL</t>
   </si>
   <si>
+    <t>CORONA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
     <t>SANDRIA</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>TELLEZ</t>
+    <t>VELAZQEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>VALENTE</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>VELAZQEZ</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>TLECUILE</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>JUAREZ</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>DE JESUS</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>ALONSO</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
   </si>
   <si>
     <t>TRUJILLO</t>
@@ -145,85 +220,103 @@
     <t>TEPEPA</t>
   </si>
   <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
     <t>VALENCIA</t>
   </si>
   <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
     <t>GAMEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ALONSO</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>HECTOR</t>
   </si>
   <si>
     <t>CRISTOPHER ALAIN</t>
   </si>
   <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
+    <t>IRVING URIEL</t>
+  </si>
+  <si>
+    <t>ANDRES NOEL</t>
+  </si>
+  <si>
     <t>OCTAVIO</t>
   </si>
   <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
     <t>JOSE MATEO</t>
   </si>
   <si>
+    <t>CRISTAL</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>ANGELES NAHOMI</t>
+  </si>
+  <si>
+    <t>LIZBET</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
+  </si>
+  <si>
+    <t>IDETH JOSELYN</t>
+  </si>
+  <si>
+    <t>JAROMI YAJAIRA</t>
+  </si>
+  <si>
+    <t>EDGAR RAMSES</t>
+  </si>
+  <si>
     <t>MONSERRATH YARETZY</t>
   </si>
   <si>
     <t>EVELYN IVETH</t>
   </si>
   <si>
-    <t>BENY ALEXANDER</t>
+    <t>PAULINA</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>ROSA ISELA</t>
   </si>
   <si>
     <t>ABIUD</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>LIZBET</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
-  </si>
-  <si>
-    <t>JAROMI YAJAIRA</t>
-  </si>
-  <si>
-    <t>EDGAR RAMSES</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
-  </si>
-  <si>
-    <t>ROSA ISELA</t>
   </si>
 </sst>
 </file>
@@ -932,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -964,22 +1057,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920002</v>
+        <v>20330051920157</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -987,22 +1080,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920013</v>
+        <v>20330051920174</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1010,22 +1103,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920021</v>
+        <v>20330051920388</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1033,16 +1126,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920029</v>
+        <v>20330051920001</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1051,113 +1144,113 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920393</v>
+        <v>20330051920002</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920183</v>
+        <v>20330051920362</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920109</v>
+        <v>20330051920013</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920111</v>
+        <v>20330051920016</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920028</v>
+        <v>20330051920363</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1171,22 +1264,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920369</v>
+        <v>20330051920021</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1194,22 +1287,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920167</v>
+        <v>20330051920025</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1217,22 +1310,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920172</v>
+        <v>20330051920028</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1240,22 +1333,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920180</v>
+        <v>20330051920029</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1263,22 +1356,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920373</v>
+        <v>20330051920037</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1286,16 +1379,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920154</v>
+        <v>20330051920369</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1309,22 +1402,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920046</v>
+        <v>20330051920162</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1332,22 +1425,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920101</v>
+        <v>20330051920167</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1355,24 +1448,277 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920107</v>
+        <v>20330051920172</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920177</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920180</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920373</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920393</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920183</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920154</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>20330051920039</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920046</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
         <v>68</v>
       </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="D27" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
         <v>11</v>
       </c>
-      <c r="G19">
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920101</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920107</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>20330051920111</v>
+      </c>
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" t="s">
+        <v>99</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20212.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="84">
   <si>
     <t>Mat</t>
   </si>
@@ -115,111 +115,81 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>BASILIO</t>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>SANDRIA</t>
+  </si>
+  <si>
+    <t>VELAZQEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>TLECUILE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
   </si>
   <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>SANDRIA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQEZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>TLECUILE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>ALONSO</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>TEPEPA</t>
-  </si>
-  <si>
     <t>CONCHE</t>
   </si>
   <si>
@@ -274,31 +244,13 @@
     <t>CRISTAL</t>
   </si>
   <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>ANGELES NAHOMI</t>
-  </si>
-  <si>
-    <t>LIZBET</t>
-  </si>
-  <si>
     <t>CRISTIAN ARTURO</t>
   </si>
   <si>
-    <t>IDETH JOSELYN</t>
-  </si>
-  <si>
-    <t>JAROMI YAJAIRA</t>
-  </si>
-  <si>
     <t>EDGAR RAMSES</t>
   </si>
   <si>
     <t>MONSERRATH YARETZY</t>
-  </si>
-  <si>
-    <t>EVELYN IVETH</t>
   </si>
   <si>
     <t>PAULINA</t>
@@ -980,13 +932,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>58.33</v>
+        <v>72.22</v>
       </c>
       <c r="H3">
         <v>5.9</v>
@@ -1025,7 +977,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1063,10 +1015,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1089,7 +1041,7 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1109,10 +1061,10 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1132,10 +1084,10 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1155,10 +1107,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1178,10 +1130,10 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1201,10 +1153,10 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1224,10 +1176,10 @@
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1247,10 +1199,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1270,10 +1222,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1293,10 +1245,10 @@
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1316,10 +1268,10 @@
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1342,7 +1294,7 @@
         <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1362,10 +1314,10 @@
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1379,16 +1331,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920369</v>
+        <v>20330051920172</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1402,16 +1354,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920162</v>
+        <v>20330051920373</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1425,16 +1377,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920167</v>
+        <v>20330051920393</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1448,16 +1400,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920172</v>
+        <v>20330051920154</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1471,22 +1423,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920177</v>
+        <v>20330051920039</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1494,22 +1446,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920180</v>
+        <v>20330051920046</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1517,22 +1469,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920373</v>
+        <v>20330051920101</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1540,22 +1492,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920393</v>
+        <v>20330051920107</v>
       </c>
       <c r="B23" t="s">
         <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1563,162 +1515,24 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920183</v>
+        <v>20330051920111</v>
       </c>
       <c r="B24" t="s">
         <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920154</v>
-      </c>
-      <c r="B25" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" t="s">
-        <v>94</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920039</v>
-      </c>
-      <c r="B26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" t="s">
-        <v>95</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920046</v>
-      </c>
-      <c r="B27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" t="s">
-        <v>68</v>
-      </c>
-      <c r="D27" t="s">
-        <v>96</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920101</v>
-      </c>
-      <c r="B28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" t="s">
-        <v>97</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920107</v>
-      </c>
-      <c r="B29" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" t="s">
-        <v>98</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>20330051920111</v>
-      </c>
-      <c r="B30" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" t="s">
-        <v>99</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>11</v>
-      </c>
-      <c r="G30">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20212.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="71">
   <si>
     <t>Mat</t>
   </si>
@@ -73,6 +73,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>ARROYO</t>
   </si>
   <si>
@@ -85,9 +88,6 @@
     <t>APALE</t>
   </si>
   <si>
-    <t>ADELL</t>
-  </si>
-  <si>
     <t>CORONA</t>
   </si>
   <si>
@@ -100,21 +100,15 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
     <t>NICIO</t>
   </si>
   <si>
-    <t>ROSAS</t>
+    <t>REYES</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
     <t>MATA</t>
   </si>
   <si>
@@ -127,12 +121,6 @@
     <t>VELAZQEZ</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
     <t>ORTIZ</t>
   </si>
   <si>
@@ -142,6 +130,9 @@
     <t>VALENTE</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
@@ -151,12 +142,6 @@
     <t>TLECUILE</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>JUAREZ</t>
   </si>
   <si>
@@ -166,16 +151,10 @@
     <t>AMADOR</t>
   </si>
   <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
+    <t>VINALAY</t>
   </si>
   <si>
     <t>CANSECO</t>
@@ -190,18 +169,15 @@
     <t>CARRERA</t>
   </si>
   <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
     <t>ROSETE</t>
   </si>
   <si>
     <t>GAMEZ</t>
   </si>
   <si>
+    <t>JOSE ABRAHAM</t>
+  </si>
+  <si>
     <t>VICTOR HUGO</t>
   </si>
   <si>
@@ -214,9 +190,6 @@
     <t>HECTOR</t>
   </si>
   <si>
-    <t>CRISTOPHER ALAIN</t>
-  </si>
-  <si>
     <t>JOSUE</t>
   </si>
   <si>
@@ -229,21 +202,15 @@
     <t>ANDRES NOEL</t>
   </si>
   <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
     <t>JOSE JULIAN</t>
   </si>
   <si>
-    <t>DULCE MARIA</t>
+    <t>ANGEL SAID</t>
   </si>
   <si>
     <t>JOSE MATEO</t>
   </si>
   <si>
-    <t>CRISTAL</t>
-  </si>
-  <si>
     <t>CRISTIAN ARTURO</t>
   </si>
   <si>
@@ -254,12 +221,6 @@
   </si>
   <si>
     <t>PAULINA</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>JESUS</t>
   </si>
   <si>
     <t>SERGIO MARIANO</t>
@@ -906,16 +867,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>65.63</v>
+        <v>71.88</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -958,13 +919,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>63.64</v>
+        <v>72.73</v>
       </c>
       <c r="H4">
         <v>5.8</v>
@@ -977,7 +938,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1009,22 +970,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920157</v>
+        <v>20330051920026</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1032,16 +993,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920174</v>
+        <v>20330051920157</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1055,16 +1016,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920388</v>
+        <v>20330051920174</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1078,39 +1039,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920001</v>
+        <v>20330051920388</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920002</v>
+        <v>20330051920001</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1130,10 +1091,10 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1153,10 +1114,10 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1176,10 +1137,10 @@
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1199,10 +1160,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1216,16 +1177,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920021</v>
+        <v>20330051920025</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1239,16 +1200,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920025</v>
+        <v>20330051920060</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1262,16 +1223,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920028</v>
+        <v>20330051920029</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1285,22 +1246,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920029</v>
+        <v>20330051920172</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1308,22 +1269,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920037</v>
+        <v>20330051920373</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1331,16 +1292,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920172</v>
+        <v>20330051920393</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1354,16 +1315,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920373</v>
+        <v>20330051920154</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1377,22 +1338,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920393</v>
+        <v>20330051920101</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1400,22 +1361,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920154</v>
+        <v>20330051920107</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1423,16 +1384,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920039</v>
+        <v>20330051920111</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1441,98 +1402,6 @@
         <v>11</v>
       </c>
       <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920046</v>
-      </c>
-      <c r="B21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920101</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920107</v>
-      </c>
-      <c r="B23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920111</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24">
         <v>1</v>
       </c>
     </row>
